--- a/excel_routes/route_GIZ_CCE_threats.xlsx
+++ b/excel_routes/route_GIZ_CCE_threats.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -541,12 +541,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>02-APR-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SM-330</t>
+          <t>SM-984</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -555,13 +555,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1471</v>
+        <v>1221</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1498</v>
+        <v>1273</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-27</v>
+        <v>-52</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -586,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>02-APR-26</t>
+          <t>28-MAY-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -600,13 +600,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1471</v>
+        <v>663</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1498</v>
+        <v>726</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-27</v>
+        <v>-63</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>09-APR-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,17 +641,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-586</t>
+          <t>Nile Air NP-142</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>686</v>
+        <v>570</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>704</v>
+        <v>581</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-18</v>
+        <v>-11</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>09-APR-26</t>
+          <t>11-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -686,17 +686,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-586</t>
+          <t>Nile Air NP-142</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>686</v>
+        <v>606</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>704</v>
+        <v>640</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-18</v>
+        <v>-34</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,17 +731,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-586</t>
+          <t>Nile Air NP-142</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1349</v>
+        <v>663</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1814</v>
+        <v>726</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-465</v>
+        <v>-63</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -752,9 +752,9 @@
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,17 +776,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-586</t>
+          <t>Nile Air NP-142</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1349</v>
+        <v>1221</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1814</v>
+        <v>1248</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-465</v>
+        <v>-27</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -797,9 +797,9 @@
       <c r="I7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1471</v>
+        <v>823</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1814</v>
+        <v>1248</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-343</v>
+        <v>-425</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -842,9 +842,9 @@
       <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,30 +866,30 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-142</t>
+          <t>Air Arabia Egypt E5-586</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1471</v>
+        <v>1076</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1814</v>
+        <v>1248</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-343</v>
+        <v>-172</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>10</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>24-MAY-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,17 +911,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-586</t>
+          <t>flyadeal F3-32</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1355</v>
+        <v>1115</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1814</v>
+        <v>1248</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-459</v>
+        <v>-133</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -932,9 +932,9 @@
       <c r="I10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>24-MAY-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,30 +956,30 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-586</t>
+          <t>flyadeal F3-32</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1355</v>
+        <v>938</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1814</v>
+        <v>1248</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-459</v>
+        <v>-310</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        <v>15</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>19-JUL-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1005,26 +1005,26 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>654</v>
+        <v>937</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>813</v>
+        <v>1248</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-159</v>
+        <v>-311</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>-10</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>19-JUL-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-586</t>
+          <t>flyadeal F3-356</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>654</v>
+        <v>965</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>813</v>
+        <v>1248</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-159</v>
+        <v>-283</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1067,9 +1067,9 @@
       <c r="I13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>19-JUL-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-586</t>
+          <t>flyadeal F3-354</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>649</v>
+        <v>965</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>813</v>
+        <v>1248</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-164</v>
+        <v>-283</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>30</v>
@@ -1112,9 +1112,9 @@
       <c r="I14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>19-JUL-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,17 +1136,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-586</t>
+          <t>flyadeal F3-32</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>649</v>
+        <v>995</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>813</v>
+        <v>1248</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-164</v>
+        <v>-253</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>30</v>
@@ -1157,9 +1157,9 @@
       <c r="I15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1188,10 +1188,10 @@
         <v>663</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>813</v>
+        <v>1248</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-150</v>
+        <v>-585</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>
@@ -1202,9 +1202,9 @@
       <c r="I16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,17 +1226,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-142</t>
+          <t>flyadeal F3-356</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>663</v>
+        <v>925</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>813</v>
+        <v>1248</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-150</v>
+        <v>-323</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>30</v>
@@ -1247,9 +1247,9 @@
       <c r="I17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-586</t>
+          <t>flyadeal F3-354</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>654</v>
+        <v>925</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>813</v>
+        <v>1248</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-159</v>
+        <v>-323</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>30</v>
@@ -1292,9 +1292,9 @@
       <c r="I18" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1320,26 +1320,26 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>654</v>
+        <v>931</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>813</v>
+        <v>1248</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-159</v>
+        <v>-317</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>-10</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>11-JUN-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-586</t>
+          <t>flyadeal F3-32</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>649</v>
+        <v>1075</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>704</v>
+        <v>1248</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-55</v>
+        <v>-173</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>30</v>
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>11-JUN-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,30 +1406,30 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-586</t>
+          <t>flyadeal F3-356</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>649</v>
+        <v>718</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>704</v>
+        <v>1248</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-55</v>
+        <v>-530</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>15</v>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>11-JUN-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1451,30 +1451,30 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-142</t>
+          <t>flyadeal F3-354</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>663</v>
+        <v>718</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>704</v>
+        <v>1248</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-41</v>
+        <v>-530</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>15</v>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>11-JUN-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,26 +1496,26 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-142</t>
+          <t>flyadeal F3-32</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>663</v>
+        <v>858</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>704</v>
+        <v>1248</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-41</v>
+        <v>-390</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -1523,276 +1523,6 @@
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>25-JUN-26</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>SM-330</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-142</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>1221</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>2107</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>-886</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>25-JUN-26</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>SM-330</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-142</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>1221</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>2107</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>-886</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>25-JUN-26</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>SM-330</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-586</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>1349</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>2107</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>-758</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>25-JUN-26</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>SM-330</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-586</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>1349</v>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>2107</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>-758</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>28-JUN-26</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>SM-330</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-586</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>1355</v>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>2107</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>-752</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>28-JUN-26</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>SM-330</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-586</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="n">
-        <v>1355</v>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>2107</v>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>-752</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_GIZ_CCE_threats.xlsx
+++ b/excel_routes/route_GIZ_CCE_threats.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -541,12 +541,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SM-984</t>
+          <t>SM-330</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -600,13 +600,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>663</v>
+        <v>606</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>726</v>
+        <v>683</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-63</v>
+        <v>-77</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -645,13 +645,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>570</v>
+        <v>606</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>581</v>
+        <v>640</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-11</v>
+        <v>-34</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>11-JUN-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -690,13 +690,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>606</v>
+        <v>1221</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>640</v>
+        <v>1248</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-34</v>
+        <v>-27</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,26 +731,26 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-142</t>
+          <t>Air Arabia Egypt E5-586</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>663</v>
+        <v>1071</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>726</v>
+        <v>1248</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-63</v>
+        <v>-177</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -780,13 +780,13 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1221</v>
+        <v>823</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>1248</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-27</v>
+        <v>-425</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -797,9 +797,9 @@
       <c r="I7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,26 +821,26 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-142</t>
+          <t>Air Arabia Egypt E5-586</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>823</v>
+        <v>633</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1248</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-425</v>
+        <v>-615</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,30 +866,30 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-586</t>
+          <t>Nile Air NP-142</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1076</v>
+        <v>663</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1248</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-172</v>
+        <v>-585</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>0</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,30 +911,30 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-32</t>
+          <t>flyadeal F3-356</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1115</v>
+        <v>748</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>1248</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-133</v>
+        <v>-500</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>15</v>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,17 +956,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-32</t>
+          <t>flyadeal F3-354</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>938</v>
+        <v>748</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1248</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-310</v>
+        <v>-500</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>15</v>
@@ -977,9 +977,9 @@
       <c r="I11" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>19-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,528 +1001,33 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-586</t>
+          <t>flyadeal F3-32</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>937</v>
+        <v>898</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>1248</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-311</v>
+        <v>-350</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        <v>15</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>19-JUL-26</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>SM-330</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-356</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>965</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>1248</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>-283</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>19-JUL-26</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>SM-330</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-354</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>965</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>1248</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>-283</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>19-JUL-26</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>SM-330</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-32</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>995</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>1248</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>-253</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>23-JUL-26</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>SM-330</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-142</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>663</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>1248</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>-585</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>23-JUL-26</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>SM-330</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-356</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>925</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>1248</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>-323</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>23-JUL-26</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>SM-330</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-354</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>925</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>1248</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>-323</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>23-JUL-26</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>SM-330</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-586</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>931</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>1248</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>-317</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I19" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>23-JUL-26</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>SM-330</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-32</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>1075</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>1248</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>-173</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>24-JUL-26</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>SM-330</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-356</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>718</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>1248</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>-530</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>24-JUL-26</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>SM-330</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-354</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>718</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>1248</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>-530</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J22" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>24-JUL-26</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>SM-330</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-32</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>858</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>1248</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>-390</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>
